--- a/tests/fixtures/MainDatabase.xlsx
+++ b/tests/fixtures/MainDatabase.xlsx
@@ -246,8 +246,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tbl_PosterOralPresentation" displayName="tbl_PosterOralPresentation" ref="B1:M5" headerRowCount="1">
-  <autoFilter ref="B1:M5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tbl_PosterOralPresentation" displayName="tbl_PosterOralPresentation" ref="B1:M6" headerRowCount="1">
+  <autoFilter ref="B1:M6"/>
   <tableColumns count="12">
     <tableColumn id="2" name="No."/>
     <tableColumn id="3" name="Title of Presentation/Topic_x000a__x000a__x000a_"/>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M5"/>
+  <dimension ref="B1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
@@ -966,6 +966,37 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Return to work after stroke</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lee Hui Min</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Presented</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>44686</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>44686</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>44687</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Test Work Rehab Day</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/MainDatabase.xlsx
+++ b/tests/fixtures/MainDatabase.xlsx
@@ -1560,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J6"/>
+  <dimension ref="B1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1777,6 +1777,40 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>Test Blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7">
+        <f>IF(INDEX(B:B,ROW()-1)="No.",1,INDEX(B:B,ROW()-1)+1)</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tan Wei Ling</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>45627</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Therapy tips video</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TestTube</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://example.com/v</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/MainDatabase.xlsx
+++ b/tests/fixtures/MainDatabase.xlsx
@@ -163,8 +163,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_PrjGeneralInfo" displayName="tbl_PrjGeneralInfo" ref="A1:AO10" headerRowCount="1">
-  <autoFilter ref="A1:AO10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_PrjGeneralInfo" displayName="tbl_PrjGeneralInfo" ref="A1:AO11" headerRowCount="1">
+  <autoFilter ref="A1:AO11"/>
   <tableColumns count="41">
     <tableColumn id="1" name="Grant Ref No"/>
     <tableColumn id="2" name="Project Name"/>
@@ -2173,7 +2173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3592,9 +3592,145 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRT-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Balance clinic evaluation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Invented project for tests</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Test Fund</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Test Group A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Intramural</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Balance
+(Test Fund)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Goh Mei Xin</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goh Mei Xin
+</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Admin Person</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>RA Person</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>On track</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>CC-TEST</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>IOG-TEST</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>IO-TEST-GRT-010</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1 RA</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="Y2:Y10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y2:Y11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>list_PrjStatus</formula1>
     </dataValidation>
   </dataValidations>
